--- a/catalog-tools/perfumes.xlsx
+++ b/catalog-tools/perfumes.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="65">
   <si>
     <t>handle</t>
   </si>
@@ -675,7 +675,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="2" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>21</v>
       </c>
@@ -721,8 +721,8 @@
       <c r="O2">
         <v>38000</v>
       </c>
-      <c r="P2" t="s">
-        <v>21</v>
+      <c r="P2">
+        <v>48000</v>
       </c>
       <c r="Q2" t="s">
         <v>33</v>
@@ -734,7 +734,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="3" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>21</v>
       </c>
@@ -780,8 +780,8 @@
       <c r="O3">
         <v>42000</v>
       </c>
-      <c r="P3" t="s">
-        <v>21</v>
+      <c r="P3">
+        <v>53000</v>
       </c>
       <c r="Q3" t="s">
         <v>33</v>
@@ -793,7 +793,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="4" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>21</v>
       </c>
@@ -839,8 +839,8 @@
       <c r="O4">
         <v>35000</v>
       </c>
-      <c r="P4" t="s">
-        <v>21</v>
+      <c r="P4">
+        <v>44000</v>
       </c>
       <c r="Q4" t="s">
         <v>33</v>
@@ -952,6 +952,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
--- a/catalog-tools/perfumes.xlsx
+++ b/catalog-tools/perfumes.xlsx
@@ -3,6 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
+  <bookViews>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896"/>
+  </bookViews>
   <sheets>
     <sheet sheetId="1" name="Perfumes" state="visible" r:id="rId4"/>
     <sheet sheetId="2" name="Stock (Shopify)" state="visible" r:id="rId5"/>
@@ -12,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="91">
   <si>
     <t>handle</t>
   </si>
@@ -77,6 +80,18 @@
     <t>stock_tester</t>
   </si>
   <si>
+    <t>casa</t>
+  </si>
+  <si>
+    <t>ocasion</t>
+  </si>
+  <si>
+    <t>estacion</t>
+  </si>
+  <si>
+    <t>anio_lanzamiento</t>
+  </si>
+  <si>
     <t/>
   </si>
   <si>
@@ -119,6 +134,9 @@
     <t>Aroma intenso y amaderado, ideal para la noche.</t>
   </si>
   <si>
+    <t>Árabe</t>
+  </si>
+  <si>
     <t>Armaf</t>
   </si>
   <si>
@@ -168,6 +186,69 @@
   </si>
   <si>
     <t>Floral dulce y cremoso, muy versátil para el día.</t>
+  </si>
+  <si>
+    <t>the-most-wanted-intense-edt-100-ml</t>
+  </si>
+  <si>
+    <t>Azzaro</t>
+  </si>
+  <si>
+    <t>The Most Wanted Intense EDT</t>
+  </si>
+  <si>
+    <t>Amaderado;Aromático;Oriental/Ámbar</t>
+  </si>
+  <si>
+    <t>Notable</t>
+  </si>
+  <si>
+    <t>Francia</t>
+  </si>
+  <si>
+    <t>Cardamomo</t>
+  </si>
+  <si>
+    <t>Toffee;Licor</t>
+  </si>
+  <si>
+    <t>Maderas ambarinas (Amberwood)</t>
+  </si>
+  <si>
+    <t>&lt;p&gt;&lt;span&gt;Azzaro The Most Wanted Parfum, la fragancia masculina que te invita a tirar la moneda y experimentar más allá de las palabras. Este perfume de hombre spicy fougère, te invita a liberar tu energía ardiente como nunca antes. El jengibre rojo se fusiona con el acorde de maderas incandescentes para una estela ardiente, mientras que el ultra adictivo acorde de caramelo mezclado con la sensual vainilla Bourbon de Madagascar, revela una firma magnética. El icónico frasco con forma de tambor de revólver color negro mate, deja ver el tono ámbar de su sensual jugo. Es un nuevo amanecer, es un nuevo juego. ¿Estás preparado para jugar y alcanzar el siguiente nivel?&lt;/span&gt;&lt;/p&gt;</t>
+  </si>
+  <si>
+    <t>Diseñador</t>
+  </si>
+  <si>
+    <t>Noche;Cita romántica;Formal/Evento</t>
+  </si>
+  <si>
+    <t>Otoño;Invierno</t>
+  </si>
+  <si>
+    <t>dior-sauvage-eau-de-parfum</t>
+  </si>
+  <si>
+    <t>Dior</t>
+  </si>
+  <si>
+    <t>Sauvage Eau de Parfum</t>
+  </si>
+  <si>
+    <t>Amaderado;Aromático;Especiado</t>
+  </si>
+  <si>
+    <t>Bergamota de Calabria;Pimienta de Sichuan</t>
+  </si>
+  <si>
+    <t>Lavanda;Anís estrellado;Nuez moscada;Pimienta rosa</t>
+  </si>
+  <si>
+    <t>Ambroxan;Vainilla;Haba tonka;Cedro</t>
+  </si>
+  <si>
+    <t>&lt;p&gt;&lt;span&gt;El frescor potente de Sauvage exhala nuevas facetas sensuales y misteriosas, renovando ampliamente la firma con una composición virtuosa. La Bergamota de Calabria, siempre tan chispeante y jugosa, incorpora nuevas notas especiadas, aportándole profundidad y sensualidad. Por su parte, la estela amaderada y ambarina del Ambroxan se envuelve en un absoluto de Vainilla de Papúa Nueva Guinea, con acentos ahumados que aportan masculinidad. Francois Demachy, Perfumista-Creador Dior, se inspiró en el desierto a la hora mágica del atardecer. El frescor de la noche junto con el ardiente aire del desierto exhala aromas intensos. En esa hora en la que los lobos aparecen y el cielo se enciende, se despliega una nueva magia. LAS PALABRAS DEL PERFUMISTA No he creado Sauvage Eau de Parfum trabajando en la potencia. Su firma es ya muy reconocible. No se trataba de exagerar ni de saturar su composición. En su lugar, me he dedicado a enriquecer cada una de sus notas dominantes para aportar nuevos colores. Francois Demachy, Dior Perfumer-Creator&lt;/span&gt;&lt;/p&gt;</t>
   </si>
   <si>
     <t>producto</t>
@@ -223,6 +304,8 @@
     </font>
     <font>
       <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="2">
@@ -590,8 +673,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:U4"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <dimension ref="A1:Y6"/>
+  <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.3" defaultColWidth="8.88671875" customHeight="1"/>
   <cols>
     <col min="1" max="2" width="14" customWidth="1"/>
     <col min="3" max="4" width="22" customWidth="1"/>
@@ -608,9 +691,10 @@
     <col min="17" max="18" width="18" customWidth="1"/>
     <col min="19" max="19" width="40" customWidth="1"/>
     <col min="20" max="21" width="13" customWidth="1"/>
+    <col min="22" max="25" width="16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:25" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -674,46 +758,58 @@
       <c r="U1" s="1" t="s">
         <v>20</v>
       </c>
+      <c r="V1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="W1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="X1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Y1" s="1" t="s">
+        <v>24</v>
+      </c>
     </row>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="B2" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="C2" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="D2" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="E2" t="s">
+        <v>29</v>
+      </c>
+      <c r="F2" t="s">
+        <v>30</v>
+      </c>
+      <c r="G2" t="s">
+        <v>31</v>
+      </c>
+      <c r="H2" t="s">
+        <v>32</v>
+      </c>
+      <c r="I2" t="s">
+        <v>33</v>
+      </c>
+      <c r="J2" t="s">
         <v>25</v>
       </c>
-      <c r="F2" t="s">
-        <v>26</v>
-      </c>
-      <c r="G2" t="s">
-        <v>27</v>
-      </c>
-      <c r="H2" t="s">
-        <v>28</v>
-      </c>
-      <c r="I2" t="s">
-        <v>29</v>
-      </c>
-      <c r="J2" t="s">
-        <v>21</v>
-      </c>
       <c r="K2" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="L2" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="M2" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="N2">
         <v>100</v>
@@ -725,54 +821,63 @@
         <v>48000</v>
       </c>
       <c r="Q2" t="s">
+        <v>37</v>
+      </c>
+      <c r="R2" t="s">
+        <v>25</v>
+      </c>
+      <c r="S2" t="s">
+        <v>38</v>
+      </c>
+      <c r="V2" t="s">
+        <v>39</v>
+      </c>
+      <c r="W2" t="s">
+        <v>25</v>
+      </c>
+      <c r="X2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="3" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>25</v>
+      </c>
+      <c r="B3" t="s">
+        <v>40</v>
+      </c>
+      <c r="C3" t="s">
+        <v>41</v>
+      </c>
+      <c r="D3" t="s">
+        <v>42</v>
+      </c>
+      <c r="E3" t="s">
+        <v>29</v>
+      </c>
+      <c r="F3" t="s">
+        <v>43</v>
+      </c>
+      <c r="G3" t="s">
+        <v>31</v>
+      </c>
+      <c r="H3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I3" t="s">
         <v>33</v>
       </c>
-      <c r="R2" t="s">
-        <v>21</v>
-      </c>
-      <c r="S2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="3" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>21</v>
-      </c>
-      <c r="B3" t="s">
-        <v>35</v>
-      </c>
-      <c r="C3" t="s">
-        <v>36</v>
-      </c>
-      <c r="D3" t="s">
-        <v>37</v>
-      </c>
-      <c r="E3" t="s">
+      <c r="J3" t="s">
         <v>25</v>
       </c>
-      <c r="F3" t="s">
-        <v>38</v>
-      </c>
-      <c r="G3" t="s">
-        <v>27</v>
-      </c>
-      <c r="H3" t="s">
-        <v>28</v>
-      </c>
-      <c r="I3" t="s">
-        <v>29</v>
-      </c>
-      <c r="J3" t="s">
-        <v>21</v>
-      </c>
       <c r="K3" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="L3" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="M3" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="N3">
         <v>105</v>
@@ -784,54 +889,57 @@
         <v>53000</v>
       </c>
       <c r="Q3" t="s">
+        <v>37</v>
+      </c>
+      <c r="R3" t="s">
+        <v>25</v>
+      </c>
+      <c r="S3" t="s">
+        <v>47</v>
+      </c>
+      <c r="V3" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="4" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>25</v>
+      </c>
+      <c r="B4" t="s">
+        <v>26</v>
+      </c>
+      <c r="C4" t="s">
+        <v>48</v>
+      </c>
+      <c r="D4" t="s">
+        <v>49</v>
+      </c>
+      <c r="E4" t="s">
+        <v>50</v>
+      </c>
+      <c r="F4" t="s">
+        <v>30</v>
+      </c>
+      <c r="G4" t="s">
+        <v>51</v>
+      </c>
+      <c r="H4" t="s">
+        <v>52</v>
+      </c>
+      <c r="I4" t="s">
         <v>33</v>
       </c>
-      <c r="R3" t="s">
-        <v>21</v>
-      </c>
-      <c r="S3" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>21</v>
-      </c>
-      <c r="B4" t="s">
-        <v>22</v>
-      </c>
-      <c r="C4" t="s">
-        <v>43</v>
-      </c>
-      <c r="D4" t="s">
-        <v>44</v>
-      </c>
-      <c r="E4" t="s">
-        <v>45</v>
-      </c>
-      <c r="F4" t="s">
-        <v>26</v>
-      </c>
-      <c r="G4" t="s">
-        <v>46</v>
-      </c>
-      <c r="H4" t="s">
-        <v>47</v>
-      </c>
-      <c r="I4" t="s">
-        <v>29</v>
-      </c>
       <c r="J4" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="K4" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="L4" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="M4" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="N4">
         <v>100</v>
@@ -843,13 +951,140 @@
         <v>44000</v>
       </c>
       <c r="Q4" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="R4" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="S4" t="s">
+        <v>56</v>
+      </c>
+      <c r="V4" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="5" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>57</v>
+      </c>
+      <c r="B5" t="s">
+        <v>58</v>
+      </c>
+      <c r="C5" t="s">
+        <v>59</v>
+      </c>
+      <c r="D5" t="s">
+        <v>60</v>
+      </c>
+      <c r="E5" t="s">
+        <v>29</v>
+      </c>
+      <c r="F5" t="s">
+        <v>43</v>
+      </c>
+      <c r="G5" t="s">
         <v>51</v>
+      </c>
+      <c r="H5" t="s">
+        <v>61</v>
+      </c>
+      <c r="I5" t="s">
+        <v>62</v>
+      </c>
+      <c r="K5" t="s">
+        <v>63</v>
+      </c>
+      <c r="L5" t="s">
+        <v>64</v>
+      </c>
+      <c r="M5" t="s">
+        <v>65</v>
+      </c>
+      <c r="N5">
+        <v>100</v>
+      </c>
+      <c r="O5">
+        <v>137750</v>
+      </c>
+      <c r="S5" t="s">
+        <v>66</v>
+      </c>
+      <c r="T5">
+        <v>3</v>
+      </c>
+      <c r="V5" t="s">
+        <v>67</v>
+      </c>
+      <c r="W5" t="s">
+        <v>68</v>
+      </c>
+      <c r="X5" t="s">
+        <v>69</v>
+      </c>
+      <c r="Y5">
+        <v>2022</v>
+      </c>
+    </row>
+    <row r="6" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>70</v>
+      </c>
+      <c r="B6" t="s">
+        <v>71</v>
+      </c>
+      <c r="C6" t="s">
+        <v>72</v>
+      </c>
+      <c r="D6" t="s">
+        <v>73</v>
+      </c>
+      <c r="E6" t="s">
+        <v>29</v>
+      </c>
+      <c r="F6" t="s">
+        <v>30</v>
+      </c>
+      <c r="G6" t="s">
+        <v>31</v>
+      </c>
+      <c r="H6" t="s">
+        <v>32</v>
+      </c>
+      <c r="I6" t="s">
+        <v>62</v>
+      </c>
+      <c r="K6" t="s">
+        <v>74</v>
+      </c>
+      <c r="L6" t="s">
+        <v>75</v>
+      </c>
+      <c r="M6" t="s">
+        <v>76</v>
+      </c>
+      <c r="N6">
+        <v>100</v>
+      </c>
+      <c r="O6">
+        <v>207000</v>
+      </c>
+      <c r="S6" t="s">
+        <v>77</v>
+      </c>
+      <c r="T6">
+        <v>3</v>
+      </c>
+      <c r="V6" t="s">
+        <v>67</v>
+      </c>
+      <c r="W6" t="s">
+        <v>68</v>
+      </c>
+      <c r="X6" t="s">
+        <v>69</v>
+      </c>
+      <c r="Y6">
+        <v>2018</v>
       </c>
     </row>
   </sheetData>
@@ -861,7 +1096,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:F4"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.3" defaultColWidth="8.88671875" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
     <col min="2" max="2" width="32" customWidth="1"/>
@@ -875,27 +1110,27 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>52</v>
+        <v>78</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>53</v>
+        <v>79</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>54</v>
+        <v>80</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>55</v>
+        <v>81</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>56</v>
+        <v>82</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>57</v>
+        <v>83</v>
       </c>
       <c r="B2" t="s">
-        <v>58</v>
+        <v>84</v>
       </c>
       <c r="C2">
         <v>5</v>
@@ -904,18 +1139,18 @@
         <v>1</v>
       </c>
       <c r="E2" t="s">
-        <v>59</v>
+        <v>85</v>
       </c>
       <c r="F2" t="s">
-        <v>60</v>
+        <v>86</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>61</v>
+        <v>87</v>
       </c>
       <c r="B3" t="s">
-        <v>62</v>
+        <v>88</v>
       </c>
       <c r="C3">
         <v>5</v>
@@ -924,18 +1159,18 @@
         <v>1</v>
       </c>
       <c r="E3" t="s">
-        <v>59</v>
+        <v>85</v>
       </c>
       <c r="F3" t="s">
-        <v>60</v>
+        <v>86</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>63</v>
+        <v>89</v>
       </c>
       <c r="B4" t="s">
-        <v>64</v>
+        <v>90</v>
       </c>
       <c r="C4">
         <v>5</v>
@@ -944,10 +1179,10 @@
         <v>1</v>
       </c>
       <c r="E4" t="s">
-        <v>59</v>
+        <v>85</v>
       </c>
       <c r="F4" t="s">
-        <v>60</v>
+        <v>86</v>
       </c>
     </row>
   </sheetData>

--- a/catalog-tools/perfumes.xlsx
+++ b/catalog-tools/perfumes.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="308" uniqueCount="185">
   <si>
     <t>handle</t>
   </si>
@@ -249,6 +249,288 @@
   </si>
   <si>
     <t>&lt;p&gt;&lt;span&gt;El frescor potente de Sauvage exhala nuevas facetas sensuales y misteriosas, renovando ampliamente la firma con una composición virtuosa. La Bergamota de Calabria, siempre tan chispeante y jugosa, incorpora nuevas notas especiadas, aportándole profundidad y sensualidad. Por su parte, la estela amaderada y ambarina del Ambroxan se envuelve en un absoluto de Vainilla de Papúa Nueva Guinea, con acentos ahumados que aportan masculinidad. Francois Demachy, Perfumista-Creador Dior, se inspiró en el desierto a la hora mágica del atardecer. El frescor de la noche junto con el ardiente aire del desierto exhala aromas intensos. En esa hora en la que los lobos aparecen y el cielo se enciende, se despliega una nueva magia. LAS PALABRAS DEL PERFUMISTA No he creado Sauvage Eau de Parfum trabajando en la potencia. Su firma es ya muy reconocible. No se trataba de exagerar ni de saturar su composición. En su lugar, me he dedicado a enriquecer cada una de sus notas dominantes para aportar nuevos colores. Francois Demachy, Dior Perfumer-Creator&lt;/span&gt;&lt;/p&gt;</t>
+  </si>
+  <si>
+    <t>Creed</t>
+  </si>
+  <si>
+    <t>Aventus</t>
+  </si>
+  <si>
+    <t>Chipre;Frutal;Amaderado</t>
+  </si>
+  <si>
+    <t>Piña;Bergamota;Grosella negra;Manzana</t>
+  </si>
+  <si>
+    <t>Abedul;Pachulí;Rosa;Jazmín</t>
+  </si>
+  <si>
+    <t>Musgo de roble;Almizcle;Ámbar gris;Vainilla</t>
+  </si>
+  <si>
+    <t>El nicho más famoso del mundo: piña jugosa sobre abedul ahumado y musgo. Versátil, elegante y reconocible al instante.</t>
+  </si>
+  <si>
+    <t>Nicho</t>
+  </si>
+  <si>
+    <t>Diario;Oficina;Formal/Evento</t>
+  </si>
+  <si>
+    <t>Todo el año</t>
+  </si>
+  <si>
+    <t>Maison Francis Kurkdjian</t>
+  </si>
+  <si>
+    <t>Baccarat Rouge 540</t>
+  </si>
+  <si>
+    <t>Oriental/Ámbar;Dulce/Gourmand</t>
+  </si>
+  <si>
+    <t>Unisex</t>
+  </si>
+  <si>
+    <t>Eterna (12h+)</t>
+  </si>
+  <si>
+    <t>Azafrán;Jazmín</t>
+  </si>
+  <si>
+    <t>Ámbar gris;Cedro</t>
+  </si>
+  <si>
+    <t>Resina de abeto;Almizcle</t>
+  </si>
+  <si>
+    <t>Ámbar dulce y mineral con azafrán: una firma luminosa que se reconoce a metros. Uno de los perfumes más deseados de la última década.</t>
+  </si>
+  <si>
+    <t>Parfums de Marly</t>
+  </si>
+  <si>
+    <t>Layton</t>
+  </si>
+  <si>
+    <t>Oriental/Ámbar;Amaderado;Aromático</t>
+  </si>
+  <si>
+    <t>Manzana;Lavanda;Bergamota;Mandarina</t>
+  </si>
+  <si>
+    <t>Geranio;Violeta;Jazmín</t>
+  </si>
+  <si>
+    <t>Vainilla;Cardamomo;Sándalo;Madera de guayaco;Pimienta</t>
+  </si>
+  <si>
+    <t>Manzana y lavanda sobre vainilla especiada: el best seller de Parfums de Marly. Presencia enorme para la noche.</t>
+  </si>
+  <si>
+    <t>Delina</t>
+  </si>
+  <si>
+    <t>Floral;Frutal</t>
+  </si>
+  <si>
+    <t>Lichi;Ruibarbo;Bergamota;Nuez moscada</t>
+  </si>
+  <si>
+    <t>Rosa turca;Peonía;Jazmín;Vainilla</t>
+  </si>
+  <si>
+    <t>Almizcle;Cachemira;Incienso;Vetiver</t>
+  </si>
+  <si>
+    <t>Rosa turca con lichi y ruibarbo: floral frutal lujoso y femenino, insignia de Parfums de Marly.</t>
+  </si>
+  <si>
+    <t>Diario;Cita romántica;Formal/Evento</t>
+  </si>
+  <si>
+    <t>Primavera;Verano</t>
+  </si>
+  <si>
+    <t>Nishane</t>
+  </si>
+  <si>
+    <t>Hacivat</t>
+  </si>
+  <si>
+    <t>Parfum/Extrait</t>
+  </si>
+  <si>
+    <t>Turquía</t>
+  </si>
+  <si>
+    <t>Piña;Pomelo;Bergamota</t>
+  </si>
+  <si>
+    <t>Jazmín;Pachulí;Cedro</t>
+  </si>
+  <si>
+    <t>Musgo de roble;Frutos secos;Notas amaderadas</t>
+  </si>
+  <si>
+    <t>Extrait turco de piña y maderas con carácter chipre: rendimiento altísimo y estela que no pasa desapercibida.</t>
+  </si>
+  <si>
+    <t>Initio</t>
+  </si>
+  <si>
+    <t>Oud for Greatness</t>
+  </si>
+  <si>
+    <t>Amaderado;Oriental/Ámbar;Especiado</t>
+  </si>
+  <si>
+    <t>Azafrán;Nuez moscada;Lavanda</t>
+  </si>
+  <si>
+    <t>Oud</t>
+  </si>
+  <si>
+    <t>Pachulí;Almizcle</t>
+  </si>
+  <si>
+    <t>Oud moderno y pulido con azafrán y lavanda: potencia de horas y estela imponente. La puerta de entrada al oud de lujo.</t>
+  </si>
+  <si>
+    <t>Noche;Formal/Evento</t>
+  </si>
+  <si>
+    <t>Xerjoff</t>
+  </si>
+  <si>
+    <t>Naxos</t>
+  </si>
+  <si>
+    <t>Dulce/Gourmand;Oriental/Ámbar;Aromático</t>
+  </si>
+  <si>
+    <t>Italia</t>
+  </si>
+  <si>
+    <t>Limón;Bergamota;Lavanda</t>
+  </si>
+  <si>
+    <t>Miel;Canela;Jazmín sambac</t>
+  </si>
+  <si>
+    <t>Hoja de tabaco;Vainilla;Haba tonka</t>
+  </si>
+  <si>
+    <t>Miel, tabaco y vainilla con arranque cítrico siciliano: dulzura adictiva de lujo italiano.</t>
+  </si>
+  <si>
+    <t>Erba Pura</t>
+  </si>
+  <si>
+    <t>Frutal;Cítrico;Dulce/Gourmand</t>
+  </si>
+  <si>
+    <t>Naranja de Sicilia;Bergamota de Calabria;Limón</t>
+  </si>
+  <si>
+    <t>Frutas dulces</t>
+  </si>
+  <si>
+    <t>Almizcle blanco;Ámbar;Vainilla de Madagascar</t>
+  </si>
+  <si>
+    <t>Explosión frutal sobre almizcle y vainilla: alegre, dulce y con un rendimiento que sorprende para lo fresco que arranca.</t>
+  </si>
+  <si>
+    <t>Diario;Casual/Fin de semana;Noche</t>
+  </si>
+  <si>
+    <t>Tiziana Terenzi</t>
+  </si>
+  <si>
+    <t>Kirke</t>
+  </si>
+  <si>
+    <t>Frutal;Chipre;Almizclado</t>
+  </si>
+  <si>
+    <t>Maracuyá;Durazno;Grosella negra;Frambuesa</t>
+  </si>
+  <si>
+    <t>Lirio de los valles;Heliotropo</t>
+  </si>
+  <si>
+    <t>Almizcle;Vainilla;Pachulí;Sándalo</t>
+  </si>
+  <si>
+    <t>Extrait de frutas doradas sobre almizcle cremoso: el favorito de culto italiano que dura de la mañana a la noche.</t>
+  </si>
+  <si>
+    <t>Diario;Cita romántica;Noche</t>
+  </si>
+  <si>
+    <t>Montale</t>
+  </si>
+  <si>
+    <t>Intense Café</t>
+  </si>
+  <si>
+    <t>Oriental/Ámbar;Dulce/Gourmand;Floral</t>
+  </si>
+  <si>
+    <t>Notas florales</t>
+  </si>
+  <si>
+    <t>Café;Rosa</t>
+  </si>
+  <si>
+    <t>Vainilla;Almizcle blanco;Ámbar</t>
+  </si>
+  <si>
+    <t>Café y rosa sobre vainilla: gourmand elegante, directo y con una estela que enamora. Puerta de entrada perfecta al nicho.</t>
+  </si>
+  <si>
+    <t>Noche;Cita romántica</t>
+  </si>
+  <si>
+    <t>Arabians Tonka</t>
+  </si>
+  <si>
+    <t>Oriental/Ámbar;Amaderado;Dulce/Gourmand</t>
+  </si>
+  <si>
+    <t>Bergamota;Azafrán</t>
+  </si>
+  <si>
+    <t>Oud;Rosa búlgara;Incienso</t>
+  </si>
+  <si>
+    <t>Haba tonka;Caña de azúcar;Musgo de roble;Almizcle blanco</t>
+  </si>
+  <si>
+    <t>Oud dulce con tonka y azúcar: denso, envolvente y de rendimiento eterno. Uno de los Montale más pedidos.</t>
+  </si>
+  <si>
+    <t>Mancera</t>
+  </si>
+  <si>
+    <t>Red Tobacco</t>
+  </si>
+  <si>
+    <t>Especiado;Amaderado;Oriental/Ámbar</t>
+  </si>
+  <si>
+    <t>Azafrán;Canela;Nuez moscada;Manzana verde</t>
+  </si>
+  <si>
+    <t>Oud;Tabaco;Incienso</t>
+  </si>
+  <si>
+    <t>Vainilla;Sándalo;Ámbar;Madera de cachemira</t>
+  </si>
+  <si>
+    <t>Tabaco especiado con oud y vainilla: calidez otoñal con proyección enorme y precio de entrada al nicho.</t>
   </si>
   <si>
     <t>producto</t>
@@ -673,7 +955,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:Y6"/>
+  <dimension ref="A1:Y18"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.3" defaultColWidth="8.88671875" customHeight="1"/>
   <cols>
     <col min="1" max="2" width="14" customWidth="1"/>
@@ -1009,9 +1291,6 @@
       <c r="S5" t="s">
         <v>66</v>
       </c>
-      <c r="T5">
-        <v>3</v>
-      </c>
       <c r="V5" t="s">
         <v>67</v>
       </c>
@@ -1071,9 +1350,6 @@
       <c r="S6" t="s">
         <v>77</v>
       </c>
-      <c r="T6">
-        <v>3</v>
-      </c>
       <c r="V6" t="s">
         <v>67</v>
       </c>
@@ -1085,6 +1361,678 @@
       </c>
       <c r="Y6">
         <v>2018</v>
+      </c>
+    </row>
+    <row r="7" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="B7" t="s">
+        <v>78</v>
+      </c>
+      <c r="C7" t="s">
+        <v>79</v>
+      </c>
+      <c r="D7" t="s">
+        <v>80</v>
+      </c>
+      <c r="E7" t="s">
+        <v>29</v>
+      </c>
+      <c r="F7" t="s">
+        <v>30</v>
+      </c>
+      <c r="G7" t="s">
+        <v>51</v>
+      </c>
+      <c r="H7" t="s">
+        <v>61</v>
+      </c>
+      <c r="I7" t="s">
+        <v>62</v>
+      </c>
+      <c r="K7" t="s">
+        <v>81</v>
+      </c>
+      <c r="L7" t="s">
+        <v>82</v>
+      </c>
+      <c r="M7" t="s">
+        <v>83</v>
+      </c>
+      <c r="N7">
+        <v>100</v>
+      </c>
+      <c r="O7">
+        <v>517500</v>
+      </c>
+      <c r="S7" t="s">
+        <v>84</v>
+      </c>
+      <c r="V7" t="s">
+        <v>85</v>
+      </c>
+      <c r="W7" t="s">
+        <v>86</v>
+      </c>
+      <c r="X7" t="s">
+        <v>87</v>
+      </c>
+      <c r="Y7">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="8" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="B8" t="s">
+        <v>88</v>
+      </c>
+      <c r="C8" t="s">
+        <v>89</v>
+      </c>
+      <c r="D8" t="s">
+        <v>90</v>
+      </c>
+      <c r="E8" t="s">
+        <v>91</v>
+      </c>
+      <c r="F8" t="s">
+        <v>30</v>
+      </c>
+      <c r="G8" t="s">
+        <v>92</v>
+      </c>
+      <c r="H8" t="s">
+        <v>32</v>
+      </c>
+      <c r="I8" t="s">
+        <v>62</v>
+      </c>
+      <c r="K8" t="s">
+        <v>93</v>
+      </c>
+      <c r="L8" t="s">
+        <v>94</v>
+      </c>
+      <c r="M8" t="s">
+        <v>95</v>
+      </c>
+      <c r="N8">
+        <v>70</v>
+      </c>
+      <c r="O8">
+        <v>555000</v>
+      </c>
+      <c r="S8" t="s">
+        <v>96</v>
+      </c>
+      <c r="V8" t="s">
+        <v>85</v>
+      </c>
+      <c r="W8" t="s">
+        <v>68</v>
+      </c>
+      <c r="X8" t="s">
+        <v>87</v>
+      </c>
+      <c r="Y8">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="9" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="B9" t="s">
+        <v>97</v>
+      </c>
+      <c r="C9" t="s">
+        <v>98</v>
+      </c>
+      <c r="D9" t="s">
+        <v>99</v>
+      </c>
+      <c r="E9" t="s">
+        <v>29</v>
+      </c>
+      <c r="F9" t="s">
+        <v>30</v>
+      </c>
+      <c r="G9" t="s">
+        <v>31</v>
+      </c>
+      <c r="H9" t="s">
+        <v>32</v>
+      </c>
+      <c r="I9" t="s">
+        <v>62</v>
+      </c>
+      <c r="K9" t="s">
+        <v>100</v>
+      </c>
+      <c r="L9" t="s">
+        <v>101</v>
+      </c>
+      <c r="M9" t="s">
+        <v>102</v>
+      </c>
+      <c r="N9">
+        <v>125</v>
+      </c>
+      <c r="O9">
+        <v>375000</v>
+      </c>
+      <c r="S9" t="s">
+        <v>103</v>
+      </c>
+      <c r="V9" t="s">
+        <v>85</v>
+      </c>
+      <c r="W9" t="s">
+        <v>68</v>
+      </c>
+      <c r="X9" t="s">
+        <v>69</v>
+      </c>
+      <c r="Y9">
+        <v>2016</v>
+      </c>
+    </row>
+    <row r="10" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="B10" t="s">
+        <v>97</v>
+      </c>
+      <c r="C10" t="s">
+        <v>104</v>
+      </c>
+      <c r="D10" t="s">
+        <v>105</v>
+      </c>
+      <c r="E10" t="s">
+        <v>50</v>
+      </c>
+      <c r="F10" t="s">
+        <v>30</v>
+      </c>
+      <c r="G10" t="s">
+        <v>51</v>
+      </c>
+      <c r="H10" t="s">
+        <v>61</v>
+      </c>
+      <c r="I10" t="s">
+        <v>62</v>
+      </c>
+      <c r="K10" t="s">
+        <v>106</v>
+      </c>
+      <c r="L10" t="s">
+        <v>107</v>
+      </c>
+      <c r="M10" t="s">
+        <v>108</v>
+      </c>
+      <c r="N10">
+        <v>75</v>
+      </c>
+      <c r="O10">
+        <v>360000</v>
+      </c>
+      <c r="S10" t="s">
+        <v>109</v>
+      </c>
+      <c r="V10" t="s">
+        <v>85</v>
+      </c>
+      <c r="W10" t="s">
+        <v>110</v>
+      </c>
+      <c r="X10" t="s">
+        <v>111</v>
+      </c>
+      <c r="Y10">
+        <v>2017</v>
+      </c>
+    </row>
+    <row r="11" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="B11" t="s">
+        <v>112</v>
+      </c>
+      <c r="C11" t="s">
+        <v>113</v>
+      </c>
+      <c r="D11" t="s">
+        <v>80</v>
+      </c>
+      <c r="E11" t="s">
+        <v>91</v>
+      </c>
+      <c r="F11" t="s">
+        <v>114</v>
+      </c>
+      <c r="G11" t="s">
+        <v>31</v>
+      </c>
+      <c r="H11" t="s">
+        <v>32</v>
+      </c>
+      <c r="I11" t="s">
+        <v>115</v>
+      </c>
+      <c r="K11" t="s">
+        <v>116</v>
+      </c>
+      <c r="L11" t="s">
+        <v>117</v>
+      </c>
+      <c r="M11" t="s">
+        <v>118</v>
+      </c>
+      <c r="N11">
+        <v>100</v>
+      </c>
+      <c r="O11">
+        <v>262500</v>
+      </c>
+      <c r="S11" t="s">
+        <v>119</v>
+      </c>
+      <c r="V11" t="s">
+        <v>85</v>
+      </c>
+      <c r="W11" t="s">
+        <v>86</v>
+      </c>
+      <c r="X11" t="s">
+        <v>87</v>
+      </c>
+      <c r="Y11">
+        <v>2017</v>
+      </c>
+    </row>
+    <row r="12" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="B12" t="s">
+        <v>120</v>
+      </c>
+      <c r="C12" t="s">
+        <v>121</v>
+      </c>
+      <c r="D12" t="s">
+        <v>122</v>
+      </c>
+      <c r="E12" t="s">
+        <v>91</v>
+      </c>
+      <c r="F12" t="s">
+        <v>30</v>
+      </c>
+      <c r="G12" t="s">
+        <v>92</v>
+      </c>
+      <c r="H12" t="s">
+        <v>32</v>
+      </c>
+      <c r="I12" t="s">
+        <v>62</v>
+      </c>
+      <c r="K12" t="s">
+        <v>123</v>
+      </c>
+      <c r="L12" t="s">
+        <v>124</v>
+      </c>
+      <c r="M12" t="s">
+        <v>125</v>
+      </c>
+      <c r="N12">
+        <v>90</v>
+      </c>
+      <c r="O12">
+        <v>360000</v>
+      </c>
+      <c r="S12" t="s">
+        <v>126</v>
+      </c>
+      <c r="V12" t="s">
+        <v>85</v>
+      </c>
+      <c r="W12" t="s">
+        <v>127</v>
+      </c>
+      <c r="X12" t="s">
+        <v>69</v>
+      </c>
+      <c r="Y12">
+        <v>2018</v>
+      </c>
+    </row>
+    <row r="13" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="B13" t="s">
+        <v>128</v>
+      </c>
+      <c r="C13" t="s">
+        <v>129</v>
+      </c>
+      <c r="D13" t="s">
+        <v>130</v>
+      </c>
+      <c r="E13" t="s">
+        <v>91</v>
+      </c>
+      <c r="F13" t="s">
+        <v>30</v>
+      </c>
+      <c r="G13" t="s">
+        <v>31</v>
+      </c>
+      <c r="H13" t="s">
+        <v>32</v>
+      </c>
+      <c r="I13" t="s">
+        <v>131</v>
+      </c>
+      <c r="K13" t="s">
+        <v>132</v>
+      </c>
+      <c r="L13" t="s">
+        <v>133</v>
+      </c>
+      <c r="M13" t="s">
+        <v>134</v>
+      </c>
+      <c r="N13">
+        <v>100</v>
+      </c>
+      <c r="O13">
+        <v>246000</v>
+      </c>
+      <c r="S13" t="s">
+        <v>135</v>
+      </c>
+      <c r="V13" t="s">
+        <v>85</v>
+      </c>
+      <c r="W13" t="s">
+        <v>127</v>
+      </c>
+      <c r="X13" t="s">
+        <v>69</v>
+      </c>
+      <c r="Y13">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="14" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="B14" t="s">
+        <v>128</v>
+      </c>
+      <c r="C14" t="s">
+        <v>136</v>
+      </c>
+      <c r="D14" t="s">
+        <v>137</v>
+      </c>
+      <c r="E14" t="s">
+        <v>91</v>
+      </c>
+      <c r="F14" t="s">
+        <v>30</v>
+      </c>
+      <c r="G14" t="s">
+        <v>31</v>
+      </c>
+      <c r="H14" t="s">
+        <v>32</v>
+      </c>
+      <c r="I14" t="s">
+        <v>131</v>
+      </c>
+      <c r="K14" t="s">
+        <v>138</v>
+      </c>
+      <c r="L14" t="s">
+        <v>139</v>
+      </c>
+      <c r="M14" t="s">
+        <v>140</v>
+      </c>
+      <c r="N14">
+        <v>100</v>
+      </c>
+      <c r="O14">
+        <v>220500</v>
+      </c>
+      <c r="S14" t="s">
+        <v>141</v>
+      </c>
+      <c r="V14" t="s">
+        <v>85</v>
+      </c>
+      <c r="W14" t="s">
+        <v>142</v>
+      </c>
+      <c r="X14" t="s">
+        <v>111</v>
+      </c>
+      <c r="Y14">
+        <v>2019</v>
+      </c>
+    </row>
+    <row r="15" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="B15" t="s">
+        <v>143</v>
+      </c>
+      <c r="C15" t="s">
+        <v>144</v>
+      </c>
+      <c r="D15" t="s">
+        <v>145</v>
+      </c>
+      <c r="E15" t="s">
+        <v>91</v>
+      </c>
+      <c r="F15" t="s">
+        <v>114</v>
+      </c>
+      <c r="G15" t="s">
+        <v>92</v>
+      </c>
+      <c r="H15" t="s">
+        <v>32</v>
+      </c>
+      <c r="I15" t="s">
+        <v>131</v>
+      </c>
+      <c r="K15" t="s">
+        <v>146</v>
+      </c>
+      <c r="L15" t="s">
+        <v>147</v>
+      </c>
+      <c r="M15" t="s">
+        <v>148</v>
+      </c>
+      <c r="N15">
+        <v>100</v>
+      </c>
+      <c r="O15">
+        <v>250500</v>
+      </c>
+      <c r="S15" t="s">
+        <v>149</v>
+      </c>
+      <c r="V15" t="s">
+        <v>85</v>
+      </c>
+      <c r="W15" t="s">
+        <v>150</v>
+      </c>
+      <c r="X15" t="s">
+        <v>87</v>
+      </c>
+      <c r="Y15">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="16" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="B16" t="s">
+        <v>151</v>
+      </c>
+      <c r="C16" t="s">
+        <v>152</v>
+      </c>
+      <c r="D16" t="s">
+        <v>153</v>
+      </c>
+      <c r="E16" t="s">
+        <v>91</v>
+      </c>
+      <c r="F16" t="s">
+        <v>30</v>
+      </c>
+      <c r="G16" t="s">
+        <v>31</v>
+      </c>
+      <c r="H16" t="s">
+        <v>32</v>
+      </c>
+      <c r="I16" t="s">
+        <v>62</v>
+      </c>
+      <c r="K16" t="s">
+        <v>154</v>
+      </c>
+      <c r="L16" t="s">
+        <v>155</v>
+      </c>
+      <c r="M16" t="s">
+        <v>156</v>
+      </c>
+      <c r="N16">
+        <v>100</v>
+      </c>
+      <c r="O16">
+        <v>126000</v>
+      </c>
+      <c r="S16" t="s">
+        <v>157</v>
+      </c>
+      <c r="V16" t="s">
+        <v>85</v>
+      </c>
+      <c r="W16" t="s">
+        <v>158</v>
+      </c>
+      <c r="X16" t="s">
+        <v>69</v>
+      </c>
+      <c r="Y16">
+        <v>2013</v>
+      </c>
+    </row>
+    <row r="17" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="B17" t="s">
+        <v>151</v>
+      </c>
+      <c r="C17" t="s">
+        <v>159</v>
+      </c>
+      <c r="D17" t="s">
+        <v>160</v>
+      </c>
+      <c r="E17" t="s">
+        <v>91</v>
+      </c>
+      <c r="F17" t="s">
+        <v>30</v>
+      </c>
+      <c r="G17" t="s">
+        <v>92</v>
+      </c>
+      <c r="H17" t="s">
+        <v>32</v>
+      </c>
+      <c r="I17" t="s">
+        <v>62</v>
+      </c>
+      <c r="K17" t="s">
+        <v>161</v>
+      </c>
+      <c r="L17" t="s">
+        <v>162</v>
+      </c>
+      <c r="M17" t="s">
+        <v>163</v>
+      </c>
+      <c r="N17">
+        <v>100</v>
+      </c>
+      <c r="O17">
+        <v>142500</v>
+      </c>
+      <c r="S17" t="s">
+        <v>164</v>
+      </c>
+      <c r="V17" t="s">
+        <v>85</v>
+      </c>
+      <c r="W17" t="s">
+        <v>127</v>
+      </c>
+      <c r="X17" t="s">
+        <v>69</v>
+      </c>
+      <c r="Y17">
+        <v>2018</v>
+      </c>
+    </row>
+    <row r="18" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="B18" t="s">
+        <v>165</v>
+      </c>
+      <c r="C18" t="s">
+        <v>166</v>
+      </c>
+      <c r="D18" t="s">
+        <v>167</v>
+      </c>
+      <c r="E18" t="s">
+        <v>91</v>
+      </c>
+      <c r="F18" t="s">
+        <v>30</v>
+      </c>
+      <c r="G18" t="s">
+        <v>92</v>
+      </c>
+      <c r="H18" t="s">
+        <v>32</v>
+      </c>
+      <c r="I18" t="s">
+        <v>62</v>
+      </c>
+      <c r="K18" t="s">
+        <v>168</v>
+      </c>
+      <c r="L18" t="s">
+        <v>169</v>
+      </c>
+      <c r="M18" t="s">
+        <v>170</v>
+      </c>
+      <c r="N18">
+        <v>120</v>
+      </c>
+      <c r="O18">
+        <v>127500</v>
+      </c>
+      <c r="S18" t="s">
+        <v>171</v>
+      </c>
+      <c r="V18" t="s">
+        <v>85</v>
+      </c>
+      <c r="W18" t="s">
+        <v>127</v>
+      </c>
+      <c r="X18" t="s">
+        <v>69</v>
+      </c>
+      <c r="Y18">
+        <v>2017</v>
       </c>
     </row>
   </sheetData>
@@ -1110,27 +2058,27 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>78</v>
+        <v>172</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>79</v>
+        <v>173</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>80</v>
+        <v>174</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>81</v>
+        <v>175</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>82</v>
+        <v>176</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>83</v>
+        <v>177</v>
       </c>
       <c r="B2" t="s">
-        <v>84</v>
+        <v>178</v>
       </c>
       <c r="C2">
         <v>5</v>
@@ -1139,18 +2087,18 @@
         <v>1</v>
       </c>
       <c r="E2" t="s">
-        <v>85</v>
+        <v>179</v>
       </c>
       <c r="F2" t="s">
-        <v>86</v>
+        <v>180</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>87</v>
+        <v>181</v>
       </c>
       <c r="B3" t="s">
-        <v>88</v>
+        <v>182</v>
       </c>
       <c r="C3">
         <v>5</v>
@@ -1159,18 +2107,18 @@
         <v>1</v>
       </c>
       <c r="E3" t="s">
-        <v>85</v>
+        <v>179</v>
       </c>
       <c r="F3" t="s">
-        <v>86</v>
+        <v>180</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>89</v>
+        <v>183</v>
       </c>
       <c r="B4" t="s">
-        <v>90</v>
+        <v>184</v>
       </c>
       <c r="C4">
         <v>5</v>
@@ -1179,10 +2127,10 @@
         <v>1</v>
       </c>
       <c r="E4" t="s">
-        <v>85</v>
+        <v>179</v>
       </c>
       <c r="F4" t="s">
-        <v>86</v>
+        <v>180</v>
       </c>
     </row>
   </sheetData>
